--- a/salidas/empresas/SLB.xlsx
+++ b/salidas/empresas/SLB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>40.9765625</v>
+        <v>40.97657775878906</v>
       </c>
       <c r="C2" t="n">
         <v>63.72499847412109</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.05200958251953</v>
+        <v>37.052001953125</v>
       </c>
       <c r="C3" t="n">
         <v>57.5</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>44.5526123046875</v>
+        <v>44.55260848999023</v>
       </c>
       <c r="C5" t="n">
         <v>69.13999938964844</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.25217437744141</v>
+        <v>42.25218200683594</v>
       </c>
       <c r="C6" t="n">
         <v>65.56999969482422</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>42.03516387939453</v>
+        <v>42.03515243530273</v>
       </c>
       <c r="C7" t="n">
         <v>65.11000061035156</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>43.15848541259766</v>
+        <v>43.15848922729492</v>
       </c>
       <c r="C8" t="n">
         <v>66.84999847412109</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.12853240966797</v>
+        <v>40.1285285949707</v>
       </c>
       <c r="C10" t="n">
         <v>62.02999877929688</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>44.3011589050293</v>
+        <v>44.30116271972656</v>
       </c>
       <c r="C12" t="n">
         <v>68.48000335693359</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.93439865112305</v>
+        <v>40.93441390991211</v>
       </c>
       <c r="C13" t="n">
         <v>63.15999984741211</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>41.14828491210938</v>
+        <v>41.14830017089844</v>
       </c>
       <c r="C14" t="n">
         <v>63.4900016784668</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>40.81306838989258</v>
+        <v>40.81306457519531</v>
       </c>
       <c r="C15" t="n">
         <v>62.79999923706055</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>44.90736770629883</v>
+        <v>44.90737533569336</v>
       </c>
       <c r="C16" t="n">
         <v>69.09999847412109</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>47.98134613037109</v>
+        <v>47.98136138916016</v>
       </c>
       <c r="C17" t="n">
         <v>73.83000183105469</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>50.60690689086914</v>
+        <v>50.60688781738281</v>
       </c>
       <c r="C18" t="n">
         <v>77.87000274658203</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>55.32545852661133</v>
+        <v>55.32542037963867</v>
       </c>
       <c r="C19" t="n">
         <v>84.94000244140625</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>61.69562149047852</v>
+        <v>61.69565200805664</v>
       </c>
       <c r="C20" t="n">
         <v>94.72000122070312</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>62.97099685668945</v>
+        <v>62.97103118896484</v>
       </c>
       <c r="C21" t="n">
         <v>96.5</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>68.51767730712891</v>
+        <v>68.51771545410156</v>
       </c>
       <c r="C22" t="n">
         <v>105</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>63.01667404174805</v>
+        <v>63.01668930053711</v>
       </c>
       <c r="C23" t="n">
         <v>96.56999969482422</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>60.98074722290039</v>
+        <v>60.98072052001953</v>
       </c>
       <c r="C24" t="n">
         <v>93.44999694824219</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>64.31172180175781</v>
+        <v>64.31172943115234</v>
       </c>
       <c r="C25" t="n">
         <v>98.37000274658203</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>49.2945442199707</v>
+        <v>49.2945556640625</v>
       </c>
       <c r="C26" t="n">
         <v>75.40000152587891</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>56.66020965576172</v>
+        <v>56.66017150878906</v>
       </c>
       <c r="C27" t="n">
         <v>86.44999694824219</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>57.02066421508789</v>
+        <v>57.02068328857422</v>
       </c>
       <c r="C28" t="n">
         <v>87</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>65.90149688720703</v>
+        <v>65.90150451660156</v>
       </c>
       <c r="C29" t="n">
         <v>100.5500030517578</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>66.28162384033203</v>
+        <v>66.2816162109375</v>
       </c>
       <c r="C30" t="n">
         <v>101.129997253418</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>70.55721282958984</v>
+        <v>70.55722808837891</v>
       </c>
       <c r="C31" t="n">
         <v>107.4300003051758</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>66.72821807861328</v>
+        <v>66.72824096679688</v>
       </c>
       <c r="C32" t="n">
         <v>101.5999984741211</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>62.01594161987305</v>
+        <v>62.01594543457031</v>
       </c>
       <c r="C33" t="n">
         <v>94.22000122070312</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>51.39913177490234</v>
+        <v>51.39910888671875</v>
       </c>
       <c r="C34" t="n">
         <v>78.08999633789062</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>33.39725112915039</v>
+        <v>33.39724731445312</v>
       </c>
       <c r="C36" t="n">
         <v>50.7400016784668</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>27.97756004333496</v>
+        <v>27.97753715515137</v>
       </c>
       <c r="C37" t="n">
         <v>42.33000183105469</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>26.97292709350586</v>
+        <v>26.97292137145996</v>
       </c>
       <c r="C38" t="n">
         <v>40.81000137329102</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>25.28183937072754</v>
+        <v>25.28182983398438</v>
       </c>
       <c r="C39" t="n">
         <v>38.06000137329102</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>26.98234176635742</v>
+        <v>26.98234558105469</v>
       </c>
       <c r="C40" t="n">
         <v>40.61999893188477</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.54223251342773</v>
+        <v>32.54222106933594</v>
       </c>
       <c r="C41" t="n">
         <v>48.9900016784668</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>38.01575469970703</v>
+        <v>38.01575088500977</v>
       </c>
       <c r="C42" t="n">
         <v>57.22999954223633</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>36.07563400268555</v>
+        <v>36.07563018798828</v>
       </c>
       <c r="C43" t="n">
         <v>54.11000061035156</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>35.66894149780273</v>
+        <v>35.6689338684082</v>
       </c>
       <c r="C44" t="n">
         <v>53.5</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>37.60673141479492</v>
+        <v>37.60672760009766</v>
       </c>
       <c r="C45" t="n">
         <v>56.20000076293945</v>
@@ -1330,7 +1342,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>41.62167739868164</v>
+        <v>41.6216926574707</v>
       </c>
       <c r="C47" t="n">
         <v>62.20000076293945</v>
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>43.70090484619141</v>
+        <v>43.70090866088867</v>
       </c>
       <c r="C49" t="n">
         <v>65.08999633789062</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.60653686523438</v>
+        <v>42.60654067993164</v>
       </c>
       <c r="C50" t="n">
         <v>63.45999908447266</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.15549850463867</v>
+        <v>41.15550231933594</v>
       </c>
       <c r="C51" t="n">
         <v>61.09999847412109</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.74515151977539</v>
+        <v>42.74515914916992</v>
       </c>
       <c r="C52" t="n">
         <v>63.45999908447266</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>48.10681915283203</v>
+        <v>48.10681533813477</v>
       </c>
       <c r="C53" t="n">
         <v>71.41999816894531</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>37.95410537719727</v>
+        <v>37.95409393310547</v>
       </c>
       <c r="C54" t="n">
         <v>56.15000152587891</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.40658187866211</v>
+        <v>37.40658950805664</v>
       </c>
       <c r="C55" t="n">
         <v>55.34000015258789</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>40.32663726806641</v>
+        <v>40.32665252685547</v>
       </c>
       <c r="C56" t="n">
         <v>59.65999984741211</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>36.18422698974609</v>
+        <v>36.18423080444336</v>
       </c>
       <c r="C57" t="n">
         <v>53.33000183105469</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>41.80218124389648</v>
+        <v>41.80216979980469</v>
       </c>
       <c r="C58" t="n">
         <v>61.61000061035156</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>47.42011642456055</v>
+        <v>47.42012405395508</v>
       </c>
       <c r="C59" t="n">
         <v>69.88999938964844</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>52.62036895751953</v>
+        <v>52.62036514282227</v>
       </c>
       <c r="C60" t="n">
         <v>77.33999633789062</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>56.81148529052734</v>
+        <v>56.81147384643555</v>
       </c>
       <c r="C61" t="n">
         <v>83.5</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>60.54677200317383</v>
+        <v>60.54673004150391</v>
       </c>
       <c r="C62" t="n">
         <v>88.98999786376953</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>63.73713302612305</v>
+        <v>63.73714447021484</v>
       </c>
       <c r="C63" t="n">
         <v>93.41999816894531</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>63.62796020507812</v>
+        <v>63.62798690795898</v>
       </c>
       <c r="C64" t="n">
         <v>93.26000213623047</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>61.23323440551758</v>
+        <v>61.23324966430664</v>
       </c>
       <c r="C65" t="n">
         <v>89.75</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>58.65585327148438</v>
+        <v>58.65583038330078</v>
       </c>
       <c r="C66" t="n">
         <v>85.72000122070312</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>59.12115478515625</v>
+        <v>59.12116241455078</v>
       </c>
       <c r="C67" t="n">
         <v>86.40000152587891</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>61.83771514892578</v>
+        <v>61.83769607543945</v>
       </c>
       <c r="C68" t="n">
         <v>90.37000274658203</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>53.62895584106445</v>
+        <v>53.6289176940918</v>
       </c>
       <c r="C69" t="n">
         <v>78.12000274658203</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>41.00429916381836</v>
+        <v>41.00429534912109</v>
       </c>
       <c r="C70" t="n">
         <v>59.72999954223633</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>50.43671798706055</v>
+        <v>50.43672561645508</v>
       </c>
       <c r="C71" t="n">
         <v>73.47000122070312</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>51.90106582641602</v>
+        <v>51.90105056762695</v>
       </c>
       <c r="C72" t="n">
         <v>75.33000183105469</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>47.06439208984375</v>
+        <v>47.06439971923828</v>
       </c>
       <c r="C73" t="n">
         <v>68.30999755859375</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>51.79080200195312</v>
+        <v>51.79081726074219</v>
       </c>
       <c r="C74" t="n">
         <v>75.16999816894531</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>53.66099166870117</v>
+        <v>53.66098403930664</v>
       </c>
       <c r="C75" t="n">
         <v>77.61000061035156</v>
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>51.26176071166992</v>
+        <v>51.26175308227539</v>
       </c>
       <c r="C77" t="n">
         <v>74.13999938964844</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.91180801391602</v>
+        <v>43.91180419921875</v>
       </c>
       <c r="C78" t="n">
         <v>63.25</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>45.06426620483398</v>
+        <v>45.06427001953125</v>
       </c>
       <c r="C79" t="n">
         <v>64.91000366210938</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>49.4727897644043</v>
+        <v>49.47281646728516</v>
       </c>
       <c r="C80" t="n">
         <v>71.26000213623047</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>50.43685150146484</v>
+        <v>50.43685531616211</v>
       </c>
       <c r="C81" t="n">
         <v>72.37999725341797</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.40201568603516</v>
+        <v>50.40200424194336</v>
       </c>
       <c r="C82" t="n">
         <v>72.33000183105469</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>48.45087814331055</v>
+        <v>48.45087432861328</v>
       </c>
       <c r="C83" t="n">
         <v>69.52999877929688</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>50.10205459594727</v>
+        <v>50.10207366943359</v>
       </c>
       <c r="C84" t="n">
         <v>71.62000274658203</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>48.47910690307617</v>
+        <v>48.47909545898438</v>
       </c>
       <c r="C85" t="n">
         <v>69.30000305175781</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>54.60020446777344</v>
+        <v>54.60019302368164</v>
       </c>
       <c r="C86" t="n">
         <v>78.05000305175781</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>54.67008209228516</v>
+        <v>54.67008590698242</v>
       </c>
       <c r="C87" t="n">
         <v>77.84999847412109</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.59142303466797</v>
+        <v>52.5914421081543</v>
       </c>
       <c r="C88" t="n">
         <v>74.88999938964844</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>52.26839828491211</v>
+        <v>52.26840209960938</v>
       </c>
       <c r="C89" t="n">
         <v>74.43000030517578</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>51.28525161743164</v>
+        <v>51.28523635864258</v>
       </c>
       <c r="C90" t="n">
         <v>73.02999877929688</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>50.53978729248047</v>
+        <v>50.53979110717773</v>
       </c>
       <c r="C91" t="n">
         <v>71.66000366210938</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.35976028442383</v>
+        <v>57.3597412109375</v>
       </c>
       <c r="C92" t="n">
         <v>81.33000183105469</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>57.30451583862305</v>
+        <v>57.30449676513672</v>
       </c>
       <c r="C93" t="n">
         <v>80.94000244140625</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>62.55778884887695</v>
+        <v>62.55777740478516</v>
       </c>
       <c r="C94" t="n">
         <v>88.36000061035156</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>66.35258483886719</v>
+        <v>66.35257720947266</v>
       </c>
       <c r="C95" t="n">
         <v>93.72000122070312</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>62.60024261474609</v>
+        <v>62.6002311706543</v>
       </c>
       <c r="C96" t="n">
         <v>88.41999816894531</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>64.02337646484375</v>
+        <v>64.02339172363281</v>
       </c>
       <c r="C97" t="n">
         <v>90.11000061035156</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>62.21872711181641</v>
+        <v>62.21870422363281</v>
       </c>
       <c r="C98" t="n">
         <v>87.56999969482422</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>66.37089538574219</v>
+        <v>66.37088775634766</v>
       </c>
       <c r="C99" t="n">
         <v>93</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>69.58238220214844</v>
+        <v>69.58235931396484</v>
       </c>
       <c r="C100" t="n">
         <v>97.5</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>72.47270965576172</v>
+        <v>72.47272491455078</v>
       </c>
       <c r="C101" t="n">
         <v>101.5500030517578</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>74.249755859375</v>
+        <v>74.24973297119141</v>
       </c>
       <c r="C102" t="n">
         <v>104.0400009155273</v>
@@ -2915,7 +2927,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2944,7 +2956,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>78.83448028564453</v>
+        <v>78.83450317382812</v>
       </c>
       <c r="C105" t="n">
         <v>109.6399993896484</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>73.11820983886719</v>
+        <v>73.11822509765625</v>
       </c>
       <c r="C106" t="n">
         <v>101.6900024414062</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>70.93954467773438</v>
+        <v>70.9395751953125</v>
       </c>
       <c r="C107" t="n">
         <v>98.66000366210938</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>61.80069351196289</v>
+        <v>61.8006706237793</v>
       </c>
       <c r="C108" t="n">
         <v>85.94999694824219</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>61.69953918457031</v>
+        <v>61.69956588745117</v>
       </c>
       <c r="C109" t="n">
         <v>85.41000366210938</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>59.51792144775391</v>
+        <v>59.51791381835938</v>
       </c>
       <c r="C110" t="n">
         <v>82.38999938964844</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>61.15143203735352</v>
+        <v>61.15142440795898</v>
       </c>
       <c r="C111" t="n">
         <v>84.16000366210938</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.62824630737305</v>
+        <v>60.62827682495117</v>
       </c>
       <c r="C112" t="n">
         <v>83.44000244140625</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>68.74448394775391</v>
+        <v>68.74449920654297</v>
       </c>
       <c r="C113" t="n">
         <v>94.61000061035156</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>65.95429992675781</v>
+        <v>65.95431518554688</v>
       </c>
       <c r="C114" t="n">
         <v>90.76999664306641</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>62.97332763671875</v>
+        <v>62.97331619262695</v>
       </c>
       <c r="C115" t="n">
         <v>86.19000244140625</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>60.51108932495117</v>
+        <v>60.51108551025391</v>
       </c>
       <c r="C116" t="n">
         <v>82.81999969482422</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>56.90320205688477</v>
+        <v>56.90319061279297</v>
       </c>
       <c r="C117" t="n">
         <v>77.37000274658203</v>
@@ -3350,7 +3362,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>57.48421478271484</v>
+        <v>57.48421859741211</v>
       </c>
       <c r="C119" t="n">
         <v>78.16000366210938</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>57.11066436767578</v>
+        <v>57.11065673828125</v>
       </c>
       <c r="C120" t="n">
         <v>77.15000152587891</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>51.63276672363281</v>
+        <v>51.63277053833008</v>
       </c>
       <c r="C121" t="n">
         <v>69.75</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>53.49821853637695</v>
+        <v>53.49820327758789</v>
       </c>
       <c r="C122" t="n">
         <v>72.26999664306641</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>53.47958755493164</v>
+        <v>53.47957229614258</v>
       </c>
       <c r="C123" t="n">
         <v>71.72000122070312</v>
@@ -3524,7 +3536,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>59.90725326538086</v>
+        <v>59.90725708007812</v>
       </c>
       <c r="C125" t="n">
         <v>80.33999633789062</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.26236724853516</v>
+        <v>57.26237487792969</v>
       </c>
       <c r="C126" t="n">
         <v>76.30000305175781</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>59.34872817993164</v>
+        <v>59.34873962402344</v>
       </c>
       <c r="C127" t="n">
         <v>79.08000183105469</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>60.4294319152832</v>
+        <v>60.42943572998047</v>
       </c>
       <c r="C128" t="n">
         <v>80.51999664306641</v>
@@ -3667,7 +3679,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3694,11 +3706,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>59.39462661743164</v>
+        <v>59.39459228515625</v>
       </c>
       <c r="C130" t="n">
         <v>78.63999938964844</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>59.08495712280273</v>
+        <v>59.08496475219727</v>
       </c>
       <c r="C131" t="n">
         <v>78.23000335693359</v>
@@ -3748,11 +3760,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.48066711425781</v>
+        <v>63.48065185546875</v>
       </c>
       <c r="C132" t="n">
         <v>84.05000305175781</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>63.78027725219727</v>
+        <v>63.78025054931641</v>
       </c>
       <c r="C133" t="n">
         <v>83.94999694824219</v>
@@ -3802,11 +3814,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>63.59792327880859</v>
+        <v>63.59793853759766</v>
       </c>
       <c r="C134" t="n">
         <v>83.70999908447266</v>
@@ -3829,7 +3841,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3856,7 +3868,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3883,7 +3895,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3910,11 +3922,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>53.57629013061523</v>
+        <v>53.5762939453125</v>
       </c>
       <c r="C138" t="n">
         <v>69.58999633789062</v>
@@ -3937,11 +3949,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>50.6892204284668</v>
+        <v>50.68921661376953</v>
       </c>
       <c r="C139" t="n">
         <v>65.83999633789062</v>
@@ -3964,11 +3976,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>52.81411361694336</v>
+        <v>52.81410980224609</v>
       </c>
       <c r="C140" t="n">
         <v>68.59999847412109</v>
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>48.89540100097656</v>
+        <v>48.8953857421875</v>
       </c>
       <c r="C141" t="n">
         <v>63.5099983215332</v>
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.13336563110352</v>
+        <v>54.13335418701172</v>
       </c>
       <c r="C142" t="n">
         <v>69.76000213623047</v>
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>49.66362380981445</v>
+        <v>49.66363143920898</v>
       </c>
       <c r="C143" t="n">
         <v>64</v>
@@ -4080,11 +4092,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>48.7712287902832</v>
+        <v>48.77123641967773</v>
       </c>
       <c r="C144" t="n">
         <v>62.84999847412109</v>
@@ -4109,11 +4121,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>52.70216751098633</v>
+        <v>52.70217514038086</v>
       </c>
       <c r="C145" t="n">
         <v>67.38999938964844</v>
@@ -4138,11 +4150,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>57.54301071166992</v>
+        <v>57.54302597045898</v>
       </c>
       <c r="C146" t="n">
         <v>73.58000183105469</v>
@@ -4165,11 +4177,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>51.69584274291992</v>
+        <v>51.69585037231445</v>
       </c>
       <c r="C147" t="n">
         <v>65.63999938964844</v>
@@ -4192,11 +4204,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.01853942871094</v>
+        <v>51.01852798461914</v>
       </c>
       <c r="C148" t="n">
         <v>64.77999877929688</v>
@@ -4219,11 +4231,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.99554443359375</v>
+        <v>53.99555206298828</v>
       </c>
       <c r="C149" t="n">
         <v>68.55999755859375</v>
@@ -4246,11 +4258,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>54.08216094970703</v>
+        <v>54.08217239379883</v>
       </c>
       <c r="C150" t="n">
         <v>68.66999816894531</v>
@@ -4273,11 +4285,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>53.17551803588867</v>
+        <v>53.17549896240234</v>
       </c>
       <c r="C151" t="n">
         <v>67.02999877929688</v>
@@ -4300,11 +4312,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>53.56423187255859</v>
+        <v>53.56421661376953</v>
       </c>
       <c r="C152" t="n">
         <v>67.51999664306641</v>
@@ -4327,7 +4339,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4354,7 +4366,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4381,11 +4393,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>41.02949905395508</v>
+        <v>41.02949142456055</v>
       </c>
       <c r="C155" t="n">
         <v>51.31000137329102</v>
@@ -4408,11 +4420,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>36.06373596191406</v>
+        <v>36.0637321472168</v>
       </c>
       <c r="C156" t="n">
         <v>45.09999847412109</v>
@@ -4435,11 +4447,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>29.16595840454102</v>
+        <v>29.16596221923828</v>
       </c>
       <c r="C157" t="n">
         <v>36.08000183105469</v>
@@ -4462,7 +4474,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4491,11 +4503,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>36.02906036376953</v>
+        <v>36.0290641784668</v>
       </c>
       <c r="C159" t="n">
         <v>44.06000137329102</v>
@@ -4520,11 +4532,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.62836837768555</v>
+        <v>35.62837982177734</v>
       </c>
       <c r="C160" t="n">
         <v>43.56999969482422</v>
@@ -4549,11 +4561,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>34.90060043334961</v>
+        <v>34.90059661865234</v>
       </c>
       <c r="C161" t="n">
         <v>42.68000030517578</v>
@@ -4578,11 +4590,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>28.36696243286133</v>
+        <v>28.3669548034668</v>
       </c>
       <c r="C162" t="n">
         <v>34.68999862670898</v>
@@ -4607,11 +4619,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>32.96086120605469</v>
+        <v>32.96085357666016</v>
       </c>
       <c r="C163" t="n">
         <v>39.7400016784668</v>
@@ -4636,11 +4648,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>33.15162658691406</v>
+        <v>33.15160751342773</v>
       </c>
       <c r="C164" t="n">
         <v>39.97000122070312</v>
@@ -4665,7 +4677,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4694,11 +4706,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>28.78481864929199</v>
+        <v>28.78482055664062</v>
       </c>
       <c r="C166" t="n">
         <v>34.16999816894531</v>
@@ -4723,11 +4735,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>27.53807640075684</v>
+        <v>27.53806686401367</v>
       </c>
       <c r="C167" t="n">
         <v>32.68999862670898</v>
@@ -4750,11 +4762,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>30.49489974975586</v>
+        <v>30.49489402770996</v>
       </c>
       <c r="C168" t="n">
         <v>36.20000076293945</v>
@@ -4777,11 +4789,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>34.33666229248047</v>
+        <v>34.3366813659668</v>
       </c>
       <c r="C169" t="n">
         <v>40.20000076293945</v>
@@ -4804,11 +4816,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>28.6224365234375</v>
+        <v>28.62243270874023</v>
       </c>
       <c r="C170" t="n">
         <v>33.5099983215332</v>
@@ -4831,11 +4843,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>23.48060417175293</v>
+        <v>23.4805965423584</v>
       </c>
       <c r="C171" t="n">
         <v>27.09000015258789</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>11.692626953125</v>
+        <v>11.69263172149658</v>
       </c>
       <c r="C172" t="n">
         <v>13.48999977111816</v>
@@ -4885,7 +4897,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4912,11 +4924,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>16.00911140441895</v>
+        <v>16.00910568237305</v>
       </c>
       <c r="C174" t="n">
         <v>18.46999931335449</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>16.04861831665039</v>
+        <v>16.04861640930176</v>
       </c>
       <c r="C175" t="n">
         <v>18.38999938964844</v>
@@ -4966,11 +4978,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>15.83044528961182</v>
+        <v>15.83044624328613</v>
       </c>
       <c r="C176" t="n">
         <v>18.13999938964844</v>
@@ -4993,11 +5005,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>16.58967781066895</v>
+        <v>16.58967590332031</v>
       </c>
       <c r="C177" t="n">
         <v>19.01000022888184</v>
@@ -5020,11 +5032,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>13.66880512237549</v>
+        <v>13.66880321502686</v>
       </c>
       <c r="C178" t="n">
         <v>15.5600004196167</v>
@@ -5047,11 +5059,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>13.12415790557861</v>
+        <v>13.12415981292725</v>
       </c>
       <c r="C179" t="n">
         <v>14.9399995803833</v>
@@ -5074,11 +5086,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>18.26313781738281</v>
+        <v>18.26313972473145</v>
       </c>
       <c r="C180" t="n">
         <v>20.79000091552734</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>19.2927360534668</v>
+        <v>19.29273223876953</v>
       </c>
       <c r="C181" t="n">
         <v>21.82999992370605</v>
@@ -5128,11 +5140,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>19.62856674194336</v>
+        <v>19.62856483459473</v>
       </c>
       <c r="C182" t="n">
         <v>22.20999908447266</v>
@@ -5155,11 +5167,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>24.78178405761719</v>
+        <v>24.78178215026855</v>
       </c>
       <c r="C183" t="n">
         <v>27.90999984741211</v>
@@ -5182,7 +5194,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5209,11 +5221,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>24.0181713104248</v>
+        <v>24.01817321777344</v>
       </c>
       <c r="C185" t="n">
         <v>27.04999923706055</v>
@@ -5236,11 +5248,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>27.81845855712891</v>
+        <v>27.81845664978027</v>
       </c>
       <c r="C186" t="n">
         <v>31.32999992370605</v>
@@ -5263,11 +5275,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>28.53609657287598</v>
+        <v>28.53609466552734</v>
       </c>
       <c r="C187" t="n">
         <v>32.0099983215332</v>
@@ -5290,11 +5302,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>25.70120811462402</v>
+        <v>25.70121002197266</v>
       </c>
       <c r="C188" t="n">
         <v>28.82999992370605</v>
@@ -5319,11 +5331,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>25.1079216003418</v>
+        <v>25.10792541503906</v>
       </c>
       <c r="C189" t="n">
         <v>28.04000091552734</v>
@@ -5348,11 +5360,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>26.54061126708984</v>
+        <v>26.54061317443848</v>
       </c>
       <c r="C190" t="n">
         <v>29.63999938964844</v>
@@ -5377,7 +5389,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5406,11 +5418,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>25.78972434997559</v>
+        <v>25.78972816467285</v>
       </c>
       <c r="C192" t="n">
         <v>28.68000030517578</v>
@@ -5435,7 +5447,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5464,7 +5476,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5493,11 +5505,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>35.39540100097656</v>
+        <v>35.39539337158203</v>
       </c>
       <c r="C195" t="n">
         <v>39.2400016784668</v>
@@ -5522,11 +5534,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>37.26257705688477</v>
+        <v>37.26258087158203</v>
       </c>
       <c r="C196" t="n">
         <v>41.31000137329102</v>
@@ -5551,11 +5563,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>35.18793106079102</v>
+        <v>35.18792343139648</v>
       </c>
       <c r="C197" t="n">
         <v>39.0099983215332</v>
@@ -5580,11 +5592,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>41.60801696777344</v>
+        <v>41.60802459716797</v>
       </c>
       <c r="C198" t="n">
         <v>45.95999908447266</v>
@@ -5609,11 +5621,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>32.37386703491211</v>
+        <v>32.37385940551758</v>
       </c>
       <c r="C199" t="n">
         <v>35.7599983215332</v>
@@ -5638,11 +5650,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>33.52360916137695</v>
+        <v>33.52360534667969</v>
       </c>
       <c r="C200" t="n">
         <v>37.02999877929688</v>
@@ -5667,11 +5679,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>34.53755569458008</v>
+        <v>34.53755950927734</v>
       </c>
       <c r="C201" t="n">
         <v>38.15000152587891</v>
@@ -5696,11 +5708,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>32.65069198608398</v>
+        <v>32.65069580078125</v>
       </c>
       <c r="C202" t="n">
         <v>35.90000152587891</v>
@@ -5725,11 +5737,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>47.32076644897461</v>
+        <v>47.32077026367188</v>
       </c>
       <c r="C203" t="n">
         <v>52.02999877929688</v>
@@ -5754,7 +5766,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5783,7 +5795,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5812,11 +5824,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>51.99985122680664</v>
+        <v>51.99985504150391</v>
       </c>
       <c r="C206" t="n">
         <v>56.97999954223633</v>
@@ -5841,7 +5853,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5870,7 +5882,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5899,7 +5911,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5928,11 +5940,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>39.27151489257812</v>
+        <v>39.27152252197266</v>
       </c>
       <c r="C210" t="n">
         <v>42.83000183105469</v>
@@ -5957,7 +5969,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5986,11 +5998,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>53.78380966186523</v>
+        <v>53.78380584716797</v>
       </c>
       <c r="C212" t="n">
         <v>58.34000015258789</v>
@@ -6015,11 +6027,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>54.35537719726562</v>
+        <v>54.35538864135742</v>
       </c>
       <c r="C213" t="n">
         <v>58.95999908447266</v>
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6073,11 +6085,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>51.52738189697266</v>
+        <v>51.52737426757812</v>
       </c>
       <c r="C215" t="n">
         <v>55.65999984741211</v>
@@ -6102,11 +6114,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>48.17615509033203</v>
+        <v>48.17615127563477</v>
       </c>
       <c r="C216" t="n">
         <v>52.04000091552734</v>
@@ -6131,11 +6143,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>48.40875625610352</v>
+        <v>48.40875244140625</v>
       </c>
       <c r="C217" t="n">
         <v>52.04000091552734</v>
@@ -6160,7 +6172,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6189,11 +6201,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>45.21372985839844</v>
+        <v>45.2137336730957</v>
       </c>
       <c r="C219" t="n">
         <v>48.33000183105469</v>
@@ -6218,7 +6230,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6247,7 +6259,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6276,11 +6288,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>42.93106460571289</v>
+        <v>42.93106079101562</v>
       </c>
       <c r="C222" t="n">
         <v>45.88999938964844</v>
@@ -6305,11 +6317,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.41928100585938</v>
+        <v>44.41927337646484</v>
       </c>
       <c r="C223" t="n">
         <v>47.18000030517578</v>
@@ -6334,11 +6346,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>45.46432495117188</v>
+        <v>45.46432876586914</v>
       </c>
       <c r="C224" t="n">
         <v>48.29000091552734</v>
@@ -6363,7 +6375,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6392,11 +6404,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>39.75381851196289</v>
+        <v>39.75382232666016</v>
       </c>
       <c r="C226" t="n">
         <v>41.95000076293945</v>
@@ -6421,7 +6433,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6450,7 +6462,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6479,7 +6491,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6508,11 +6520,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>38.41325378417969</v>
+        <v>38.41325759887695</v>
       </c>
       <c r="C230" t="n">
         <v>40.27999877929688</v>
@@ -6537,11 +6549,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>40.00590515136719</v>
+        <v>40.00590896606445</v>
       </c>
       <c r="C231" t="n">
         <v>41.65999984741211</v>
@@ -6566,7 +6578,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6595,11 +6607,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>31.9298152923584</v>
+        <v>31.92982292175293</v>
       </c>
       <c r="C233" t="n">
         <v>33.25</v>
@@ -6624,11 +6636,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>31.73775863647461</v>
+        <v>31.73776054382324</v>
       </c>
       <c r="C234" t="n">
         <v>33.04999923706055</v>
@@ -6653,7 +6665,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6682,7 +6694,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6711,7 +6723,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6740,11 +6752,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>33.54978561401367</v>
+        <v>33.54978942871094</v>
       </c>
       <c r="C238" t="n">
         <v>34.36999893188477</v>
@@ -6769,7 +6781,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6798,11 +6810,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>35.37516021728516</v>
+        <v>35.37516403198242</v>
       </c>
       <c r="C240" t="n">
         <v>36.2400016784668</v>
@@ -6827,7 +6839,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6856,11 +6868,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>47.59854888916016</v>
+        <v>47.59854507446289</v>
       </c>
       <c r="C242" t="n">
         <v>48.38000106811523</v>
@@ -6885,7 +6897,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6914,7 +6926,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6943,11 +6955,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>56.29125595092773</v>
+        <v>56.29125213623047</v>
       </c>
       <c r="C245" t="n">
         <v>56.88000106811523</v>
@@ -6972,7 +6984,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7001,7 +7013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7030,7 +7042,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7059,7 +7071,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7088,32 +7100,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>51.86999893188477</v>
+        <v>51.43000030517578</v>
       </c>
       <c r="C250" t="n">
-        <v>51.86999893188477</v>
+        <v>51.43000030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>220522200</v>
+        <v>229957900</v>
       </c>
       <c r="E250" t="n">
         <v>2.050000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>25.30243850335841</v>
+        <v>25.087805026915</v>
       </c>
       <c r="G250" t="n">
         <v>1484143231</v>
       </c>
       <c r="H250" t="n">
-        <v>76982507806.73401</v>
+        <v>76329486823.25458</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1485855242228976</v>
+        <v>0.1549431990098805</v>
       </c>
     </row>
   </sheetData>
@@ -7145,75 +7157,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7249,13 +7261,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7291,13 +7303,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I10" t="n">
         <v>3.38</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K10" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I11" t="n">
         <v>3.51</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K11" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I12" t="n">
         <v>3.81</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K12" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I13" t="n">
         <v>3.39</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K13" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I14" t="n">
         <v>3.67</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="K14" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I15" t="n">
         <v>3.95</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K15" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I16" t="n">
         <v>4.02</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K16" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I17" t="n">
         <v>4.13</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="K17" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I18" t="n">
         <v>4.1</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="K18" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I19" t="n">
         <v>4.07</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K19" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I20" t="n">
         <v>4.59</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K20" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I21" t="n">
         <v>4.81</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="K21" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I22" t="n">
         <v>5.05</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="K22" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I23" t="n">
         <v>5.32</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="K23" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I24" t="n">
         <v>4.96</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K24" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I25" t="n">
         <v>5.16</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="K25" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42033</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I26" t="n">
         <v>4.16</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42033</v>
       </c>
       <c r="K26" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I27" t="n">
         <v>3.71</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="K27" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I28" t="n">
         <v>3.38</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="K28" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I29" t="n">
         <v>2.67</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="K29" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I30" t="n">
         <v>1.63</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="K30" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I31" t="n">
         <v>1.27</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K31" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I32" t="n">
         <v>-1.17</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K32" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I33" t="n">
         <v>-1.82</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K33" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42760</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I34" t="n">
         <v>-1.24</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42760</v>
       </c>
       <c r="K34" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I35" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K35" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I36" t="n">
         <v>0.07000000000000049</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K36" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I37" t="n">
         <v>0.3300000000000005</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="K37" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43124</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I38" t="n">
         <v>-1.08</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43124</v>
       </c>
       <c r="K38" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I39" t="n">
         <v>-0.8999999999999998</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K39" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I40" t="n">
         <v>-0.5399999999999998</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K40" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I41" t="n">
         <v>-0.4699999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K41" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43488</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I42" t="n">
         <v>1.53</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43488</v>
       </c>
       <c r="K42" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I43" t="n">
         <v>1.45</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K43" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I44" t="n">
         <v>1.49</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="K44" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I45" t="n">
         <v>-7.19</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="K45" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43852</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I46" t="n">
         <v>-7.32</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43852</v>
       </c>
       <c r="K46" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43943</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I47" t="n">
         <v>-12.94</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43943</v>
       </c>
       <c r="K47" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I48" t="n">
         <v>-15.76</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K48" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44125</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I49" t="n">
         <v>-7.6</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44125</v>
       </c>
       <c r="K49" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I50" t="n">
         <v>-7.569999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="K50" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I51" t="n">
         <v>-2.039999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K51" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I52" t="n">
         <v>0.7300000000000011</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K52" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I53" t="n">
         <v>1.180000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K53" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44587</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I54" t="n">
         <v>1.320000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44587</v>
       </c>
       <c r="K54" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I55" t="n">
         <v>1.470000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="K55" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I56" t="n">
         <v>1.840000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K56" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I57" t="n">
         <v>2.080000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K57" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I58" t="n">
         <v>2.390000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="K58" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I59" t="n">
         <v>2.680000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K59" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I60" t="n">
         <v>2.73</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K60" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I61" t="n">
         <v>2.880000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K61" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45315</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I62" t="n">
         <v>2.910000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45315</v>
       </c>
       <c r="K62" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I63" t="n">
         <v>3.000000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="K63" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I64" t="n">
         <v>3.050000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="K64" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I65" t="n">
         <v>3.100000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="K65" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10152,7 +10164,7 @@
       <c r="I66" t="n">
         <v>3.110000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="K66" t="n">
@@ -10165,13 +10177,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10198,7 +10210,7 @@
       <c r="I67" t="n">
         <v>2.950000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K67" t="n">
@@ -10211,13 +10223,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10244,7 +10256,7 @@
       <c r="I68" t="n">
         <v>2.920000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K68" t="n">
@@ -10257,13 +10269,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10290,7 +10302,7 @@
       <c r="I69" t="n">
         <v>2.590000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="K69" t="n">
@@ -10303,13 +10315,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10336,7 +10348,7 @@
       <c r="I70" t="n">
         <v>2.350000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="K70" t="n">
@@ -10349,13 +10361,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10382,7 +10394,7 @@
       <c r="I71" t="n">
         <v>2.270000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K71" t="n">
@@ -10395,13 +10407,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10428,7 +10440,7 @@
       <c r="I72" t="n">
         <v>2.050000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="K72" t="n">
@@ -10465,52 +10477,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="C2" t="n">
@@ -10539,10 +10551,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="C3" t="n">
@@ -10571,10 +10583,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40214</v>
       </c>
       <c r="C4" t="n">
@@ -10603,10 +10615,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="C5" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="C6" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C7" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="C8" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C9" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C10" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C11" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="C12" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C13" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C14" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C15" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="C16" t="n">
@@ -10987,10 +10999,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C17" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11051,10 +11063,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="C19" t="n">
@@ -11083,10 +11095,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="C20" t="n">
@@ -11115,10 +11127,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C21" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C22" t="n">
@@ -11179,10 +11191,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="C23" t="n">
@@ -11211,10 +11223,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42033</v>
       </c>
       <c r="C24" t="n">
@@ -11243,10 +11255,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="C25" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="C26" t="n">
@@ -11307,10 +11319,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="C27" t="n">
@@ -11339,10 +11351,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="C28" t="n">
@@ -11371,10 +11383,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11403,10 +11415,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11435,10 +11447,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C31" t="n">
@@ -11467,10 +11479,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42760</v>
       </c>
       <c r="C32" t="n">
@@ -11499,10 +11511,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C33" t="n">
@@ -11531,10 +11543,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C34" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="C35" t="n">
@@ -11595,10 +11607,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43124</v>
       </c>
       <c r="C36" t="n">
@@ -11627,10 +11639,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C37" t="n">
@@ -11659,10 +11671,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C38" t="n">
@@ -11691,10 +11703,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C39" t="n">
@@ -11723,10 +11735,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43488</v>
       </c>
       <c r="C40" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11787,10 +11799,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="C42" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="C43" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43852</v>
       </c>
       <c r="C44" t="n">
@@ -11883,10 +11895,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43943</v>
       </c>
       <c r="C45" t="n">
@@ -11915,10 +11927,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44125</v>
       </c>
       <c r="C47" t="n">
@@ -11979,10 +11991,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="C48" t="n">
@@ -12011,10 +12023,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -12043,10 +12055,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -12107,10 +12119,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44587</v>
       </c>
       <c r="C52" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="C53" t="n">
@@ -12171,10 +12183,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C54" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C55" t="n">
@@ -12235,10 +12247,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="C56" t="n">
@@ -12267,10 +12279,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C57" t="n">
@@ -12299,10 +12311,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C58" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C59" t="n">
@@ -12363,10 +12375,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45315</v>
       </c>
       <c r="C60" t="n">
@@ -12395,10 +12407,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="C61" t="n">
@@ -12427,10 +12439,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C62" t="n">
@@ -12459,10 +12471,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C63" t="n">
@@ -12491,10 +12503,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45679</v>
       </c>
       <c r="C64" t="n">
@@ -12523,10 +12535,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C65" t="n">
@@ -12555,10 +12567,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C66" t="n">
@@ -12587,10 +12599,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="C67" t="n">
@@ -12619,10 +12631,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="C68" t="n">
@@ -12651,10 +12663,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C69" t="n">
@@ -12683,10 +12695,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="C70" t="n">
@@ -12733,12 +12745,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/SLB.xlsx
+++ b/salidas/empresas/SLB.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>40.97657775878906</v>
+        <v>40.97658920288086</v>
       </c>
       <c r="C2" t="n">
         <v>63.72499847412109</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>40.77975845336914</v>
+        <v>40.77975082397461</v>
       </c>
       <c r="C4" t="n">
         <v>63.28499984741211</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>44.55260848999023</v>
+        <v>44.55261611938477</v>
       </c>
       <c r="C5" t="n">
         <v>69.13999938964844</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.25218200683594</v>
+        <v>42.25217819213867</v>
       </c>
       <c r="C6" t="n">
         <v>65.56999969482422</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>43.15848922729492</v>
+        <v>43.15850067138672</v>
       </c>
       <c r="C8" t="n">
         <v>66.84999847412109</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>39.57541275024414</v>
+        <v>39.57539749145508</v>
       </c>
       <c r="C9" t="n">
         <v>61.29999923706055</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.1285285949707</v>
+        <v>40.12853240966797</v>
       </c>
       <c r="C10" t="n">
         <v>62.02999877929688</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>40.81306457519531</v>
+        <v>40.81305313110352</v>
       </c>
       <c r="C15" t="n">
         <v>62.79999923706055</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>44.90737533569336</v>
+        <v>44.90736770629883</v>
       </c>
       <c r="C16" t="n">
         <v>69.09999847412109</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>47.98136138916016</v>
+        <v>47.98135375976562</v>
       </c>
       <c r="C17" t="n">
         <v>73.83000183105469</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>50.60688781738281</v>
+        <v>50.60691070556641</v>
       </c>
       <c r="C18" t="n">
         <v>77.87000274658203</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>55.32542037963867</v>
+        <v>55.32545471191406</v>
       </c>
       <c r="C19" t="n">
         <v>84.94000244140625</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>61.69565200805664</v>
+        <v>61.69563293457031</v>
       </c>
       <c r="C20" t="n">
         <v>94.72000122070312</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>62.97103118896484</v>
+        <v>62.97100830078125</v>
       </c>
       <c r="C21" t="n">
         <v>96.5</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>68.51771545410156</v>
+        <v>68.51767730712891</v>
       </c>
       <c r="C22" t="n">
         <v>105</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>63.01668930053711</v>
+        <v>63.01669692993164</v>
       </c>
       <c r="C23" t="n">
         <v>96.56999969482422</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>60.98072052001953</v>
+        <v>60.98073196411133</v>
       </c>
       <c r="C24" t="n">
         <v>93.44999694824219</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>64.31172943115234</v>
+        <v>64.31170654296875</v>
       </c>
       <c r="C25" t="n">
         <v>98.37000274658203</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>49.2945556640625</v>
+        <v>49.29453277587891</v>
       </c>
       <c r="C26" t="n">
         <v>75.40000152587891</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>56.66017150878906</v>
+        <v>56.66020965576172</v>
       </c>
       <c r="C27" t="n">
         <v>86.44999694824219</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>57.02068328857422</v>
+        <v>57.02067184448242</v>
       </c>
       <c r="C28" t="n">
         <v>87</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>65.90150451660156</v>
+        <v>65.90147399902344</v>
       </c>
       <c r="C29" t="n">
         <v>100.5500030517578</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>66.2816162109375</v>
+        <v>66.28162384033203</v>
       </c>
       <c r="C30" t="n">
         <v>101.129997253418</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>70.55722808837891</v>
+        <v>70.55720520019531</v>
       </c>
       <c r="C31" t="n">
         <v>107.4300003051758</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>66.72824096679688</v>
+        <v>66.72820281982422</v>
       </c>
       <c r="C32" t="n">
         <v>101.5999984741211</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>62.01594543457031</v>
+        <v>62.01596069335938</v>
       </c>
       <c r="C33" t="n">
         <v>94.22000122070312</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>51.39910888671875</v>
+        <v>51.39911270141602</v>
       </c>
       <c r="C34" t="n">
         <v>78.08999633789062</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>33.99622344970703</v>
+        <v>33.99621200561523</v>
       </c>
       <c r="C35" t="n">
         <v>51.65000152587891</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>27.97753715515137</v>
+        <v>27.97754859924316</v>
       </c>
       <c r="C37" t="n">
         <v>42.33000183105469</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>26.97292137145996</v>
+        <v>26.97292709350586</v>
       </c>
       <c r="C38" t="n">
         <v>40.81000137329102</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>25.28182983398438</v>
+        <v>25.28183937072754</v>
       </c>
       <c r="C39" t="n">
         <v>38.06000137329102</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>26.98234558105469</v>
+        <v>26.98234939575195</v>
       </c>
       <c r="C40" t="n">
         <v>40.61999893188477</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.54222106933594</v>
+        <v>32.54223251342773</v>
       </c>
       <c r="C41" t="n">
         <v>48.9900016784668</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>37.60672760009766</v>
+        <v>37.60673141479492</v>
       </c>
       <c r="C45" t="n">
         <v>56.20000076293945</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>41.6216926574707</v>
+        <v>41.62170791625977</v>
       </c>
       <c r="C47" t="n">
         <v>62.20000076293945</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>42.89523315429688</v>
+        <v>42.89524841308594</v>
       </c>
       <c r="C48" t="n">
         <v>63.88999938964844</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>43.70090866088867</v>
+        <v>43.70089721679688</v>
       </c>
       <c r="C49" t="n">
         <v>65.08999633789062</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.60654067993164</v>
+        <v>42.60654449462891</v>
       </c>
       <c r="C50" t="n">
         <v>63.45999908447266</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.15550231933594</v>
+        <v>41.15550994873047</v>
       </c>
       <c r="C51" t="n">
         <v>61.09999847412109</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>48.10681533813477</v>
+        <v>48.10680770874023</v>
       </c>
       <c r="C53" t="n">
         <v>71.41999816894531</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>37.95409393310547</v>
+        <v>37.95408630371094</v>
       </c>
       <c r="C54" t="n">
         <v>56.15000152587891</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.40658950805664</v>
+        <v>37.40659332275391</v>
       </c>
       <c r="C55" t="n">
         <v>55.34000015258789</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>40.32665252685547</v>
+        <v>40.3266487121582</v>
       </c>
       <c r="C56" t="n">
         <v>59.65999984741211</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>36.18423080444336</v>
+        <v>36.18422317504883</v>
       </c>
       <c r="C57" t="n">
         <v>53.33000183105469</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>41.80216979980469</v>
+        <v>41.80215835571289</v>
       </c>
       <c r="C58" t="n">
         <v>61.61000061035156</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>47.42012405395508</v>
+        <v>47.42011260986328</v>
       </c>
       <c r="C59" t="n">
         <v>69.88999938964844</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>52.62036514282227</v>
+        <v>52.62035751342773</v>
       </c>
       <c r="C60" t="n">
         <v>77.33999633789062</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>56.81147384643555</v>
+        <v>56.81147766113281</v>
       </c>
       <c r="C61" t="n">
         <v>83.5</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>60.54673004150391</v>
+        <v>60.5467643737793</v>
       </c>
       <c r="C62" t="n">
         <v>88.98999786376953</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>63.73714447021484</v>
+        <v>63.73714065551758</v>
       </c>
       <c r="C63" t="n">
         <v>93.41999816894531</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>63.62798690795898</v>
+        <v>63.62798309326172</v>
       </c>
       <c r="C64" t="n">
         <v>93.26000213623047</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>61.23324966430664</v>
+        <v>61.23323822021484</v>
       </c>
       <c r="C65" t="n">
         <v>89.75</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>58.65583038330078</v>
+        <v>58.65585708618164</v>
       </c>
       <c r="C66" t="n">
         <v>85.72000122070312</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>59.12116241455078</v>
+        <v>59.12115097045898</v>
       </c>
       <c r="C67" t="n">
         <v>86.40000152587891</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>61.83769607543945</v>
+        <v>61.83771896362305</v>
       </c>
       <c r="C68" t="n">
         <v>90.37000274658203</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>53.6289176940918</v>
+        <v>53.62894439697266</v>
       </c>
       <c r="C69" t="n">
         <v>78.12000274658203</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>51.90105056762695</v>
+        <v>51.90104675292969</v>
       </c>
       <c r="C72" t="n">
         <v>75.33000183105469</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>51.79081726074219</v>
+        <v>51.79082107543945</v>
       </c>
       <c r="C74" t="n">
         <v>75.16999816894531</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>53.66098403930664</v>
+        <v>53.66098785400391</v>
       </c>
       <c r="C75" t="n">
         <v>77.61000061035156</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>48.35088729858398</v>
+        <v>48.35088348388672</v>
       </c>
       <c r="C76" t="n">
         <v>69.93000030517578</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>51.26175308227539</v>
+        <v>51.26176071166992</v>
       </c>
       <c r="C77" t="n">
         <v>74.13999938964844</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.91180419921875</v>
+        <v>43.91179656982422</v>
       </c>
       <c r="C78" t="n">
         <v>63.25</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>45.06427001953125</v>
+        <v>45.06428146362305</v>
       </c>
       <c r="C79" t="n">
         <v>64.91000366210938</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.40200424194336</v>
+        <v>50.40202713012695</v>
       </c>
       <c r="C82" t="n">
         <v>72.33000183105469</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>48.45087432861328</v>
+        <v>48.45088958740234</v>
       </c>
       <c r="C83" t="n">
         <v>69.52999877929688</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>50.10207366943359</v>
+        <v>50.10204696655273</v>
       </c>
       <c r="C84" t="n">
         <v>71.62000274658203</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>48.47909545898438</v>
+        <v>48.47910308837891</v>
       </c>
       <c r="C85" t="n">
         <v>69.30000305175781</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>54.60019302368164</v>
+        <v>54.60018539428711</v>
       </c>
       <c r="C86" t="n">
         <v>78.05000305175781</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>54.67008590698242</v>
+        <v>54.67008972167969</v>
       </c>
       <c r="C87" t="n">
         <v>77.84999847412109</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>52.26840209960938</v>
+        <v>52.26838684082031</v>
       </c>
       <c r="C89" t="n">
         <v>74.43000030517578</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>51.28523635864258</v>
+        <v>51.28525161743164</v>
       </c>
       <c r="C90" t="n">
         <v>73.02999877929688</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.3597412109375</v>
+        <v>57.35974502563477</v>
       </c>
       <c r="C92" t="n">
         <v>81.33000183105469</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>57.30449676513672</v>
+        <v>57.30451583862305</v>
       </c>
       <c r="C93" t="n">
         <v>80.94000244140625</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>62.55777740478516</v>
+        <v>62.55774688720703</v>
       </c>
       <c r="C94" t="n">
         <v>88.36000061035156</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>62.6002311706543</v>
+        <v>62.60025787353516</v>
       </c>
       <c r="C96" t="n">
         <v>88.41999816894531</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>64.02339172363281</v>
+        <v>64.02338409423828</v>
       </c>
       <c r="C97" t="n">
         <v>90.11000061035156</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>62.21870422363281</v>
+        <v>62.21871185302734</v>
       </c>
       <c r="C98" t="n">
         <v>87.56999969482422</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>66.37088775634766</v>
+        <v>66.37088012695312</v>
       </c>
       <c r="C99" t="n">
         <v>93</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>69.58235931396484</v>
+        <v>69.58238220214844</v>
       </c>
       <c r="C100" t="n">
         <v>97.5</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>74.24973297119141</v>
+        <v>74.24974822998047</v>
       </c>
       <c r="C102" t="n">
         <v>104.0400009155273</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>84.50170135498047</v>
+        <v>84.50168609619141</v>
       </c>
       <c r="C103" t="n">
         <v>117.9499969482422</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>77.65271759033203</v>
+        <v>77.6527099609375</v>
       </c>
       <c r="C104" t="n">
         <v>108.3899993896484</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>78.83450317382812</v>
+        <v>78.83451843261719</v>
       </c>
       <c r="C105" t="n">
         <v>109.6399993896484</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>73.11822509765625</v>
+        <v>73.11821746826172</v>
       </c>
       <c r="C106" t="n">
         <v>101.6900024414062</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>70.9395751953125</v>
+        <v>70.93955230712891</v>
       </c>
       <c r="C107" t="n">
         <v>98.66000366210938</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>61.8006706237793</v>
+        <v>61.80069351196289</v>
       </c>
       <c r="C108" t="n">
         <v>85.94999694824219</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>61.69956588745117</v>
+        <v>61.69953155517578</v>
       </c>
       <c r="C109" t="n">
         <v>85.41000366210938</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>59.51791381835938</v>
+        <v>59.51792907714844</v>
       </c>
       <c r="C110" t="n">
         <v>82.38999938964844</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.62827682495117</v>
+        <v>60.62824630737305</v>
       </c>
       <c r="C112" t="n">
         <v>83.44000244140625</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>68.74449920654297</v>
+        <v>68.74447631835938</v>
       </c>
       <c r="C113" t="n">
         <v>94.61000061035156</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>65.95431518554688</v>
+        <v>65.95427703857422</v>
       </c>
       <c r="C114" t="n">
         <v>90.76999664306641</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>62.97331619262695</v>
+        <v>62.97332382202148</v>
       </c>
       <c r="C115" t="n">
         <v>86.19000244140625</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>60.51108551025391</v>
+        <v>60.51107025146484</v>
       </c>
       <c r="C116" t="n">
         <v>82.81999969482422</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>56.90319061279297</v>
+        <v>56.90320587158203</v>
       </c>
       <c r="C117" t="n">
         <v>77.37000274658203</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>50.72526168823242</v>
+        <v>50.72526550292969</v>
       </c>
       <c r="C118" t="n">
         <v>68.97000122070312</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>57.48421859741211</v>
+        <v>57.48421478271484</v>
       </c>
       <c r="C119" t="n">
         <v>78.16000366210938</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>57.11065673828125</v>
+        <v>57.11066055297852</v>
       </c>
       <c r="C120" t="n">
         <v>77.15000152587891</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>51.63277053833008</v>
+        <v>51.63278198242188</v>
       </c>
       <c r="C121" t="n">
         <v>69.75</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>53.49820327758789</v>
+        <v>53.49821090698242</v>
       </c>
       <c r="C122" t="n">
         <v>72.26999664306641</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>53.47957229614258</v>
+        <v>53.47956848144531</v>
       </c>
       <c r="C123" t="n">
         <v>71.72000122070312</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>54.99327850341797</v>
+        <v>54.9932746887207</v>
       </c>
       <c r="C124" t="n">
         <v>73.75</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>59.90725708007812</v>
+        <v>59.9072380065918</v>
       </c>
       <c r="C125" t="n">
         <v>80.33999633789062</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.26237487792969</v>
+        <v>57.26239013671875</v>
       </c>
       <c r="C126" t="n">
         <v>76.30000305175781</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>59.34873962402344</v>
+        <v>59.34874725341797</v>
       </c>
       <c r="C127" t="n">
         <v>79.08000183105469</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>60.42943572998047</v>
+        <v>60.42941665649414</v>
       </c>
       <c r="C128" t="n">
         <v>80.51999664306641</v>
@@ -3683,7 +3683,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>59.28871917724609</v>
+        <v>59.28869247436523</v>
       </c>
       <c r="C129" t="n">
         <v>79</v>
@@ -3710,7 +3710,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>59.39459228515625</v>
+        <v>59.39462661743164</v>
       </c>
       <c r="C130" t="n">
         <v>78.63999938964844</v>
@@ -3764,7 +3764,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.48065185546875</v>
+        <v>63.48065567016602</v>
       </c>
       <c r="C132" t="n">
         <v>84.05000305175781</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>63.78025054931641</v>
+        <v>63.78025817871094</v>
       </c>
       <c r="C133" t="n">
         <v>83.94999694824219</v>
@@ -3818,7 +3818,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>63.59793853759766</v>
+        <v>63.59792709350586</v>
       </c>
       <c r="C134" t="n">
         <v>83.70999908447266</v>
@@ -3845,7 +3845,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>61.42660903930664</v>
+        <v>61.42661285400391</v>
       </c>
       <c r="C135" t="n">
         <v>80.36000061035156</v>
@@ -3872,7 +3872,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>59.6990852355957</v>
+        <v>59.69907379150391</v>
       </c>
       <c r="C136" t="n">
         <v>78.09999847412109</v>
@@ -3899,7 +3899,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>55.48727416992188</v>
+        <v>55.48728179931641</v>
       </c>
       <c r="C137" t="n">
         <v>72.58999633789062</v>
@@ -3953,7 +3953,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>50.68921661376953</v>
+        <v>50.68923187255859</v>
       </c>
       <c r="C139" t="n">
         <v>65.83999633789062</v>
@@ -3980,7 +3980,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>52.81410980224609</v>
+        <v>52.81410598754883</v>
       </c>
       <c r="C140" t="n">
         <v>68.59999847412109</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>48.8953857421875</v>
+        <v>48.89539337158203</v>
       </c>
       <c r="C141" t="n">
         <v>63.5099983215332</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.13335418701172</v>
+        <v>54.13336563110352</v>
       </c>
       <c r="C142" t="n">
         <v>69.76000213623047</v>
@@ -4067,7 +4067,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>49.66363143920898</v>
+        <v>49.66362762451172</v>
       </c>
       <c r="C143" t="n">
         <v>64</v>
@@ -4125,7 +4125,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>52.70217514038086</v>
+        <v>52.70217132568359</v>
       </c>
       <c r="C145" t="n">
         <v>67.38999938964844</v>
@@ -4154,7 +4154,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>57.54302597045898</v>
+        <v>57.54304504394531</v>
       </c>
       <c r="C146" t="n">
         <v>73.58000183105469</v>
@@ -4181,7 +4181,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>51.69585037231445</v>
+        <v>51.69584655761719</v>
       </c>
       <c r="C147" t="n">
         <v>65.63999938964844</v>
@@ -4208,7 +4208,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.01852798461914</v>
+        <v>51.01853942871094</v>
       </c>
       <c r="C148" t="n">
         <v>64.77999877929688</v>
@@ -4235,7 +4235,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.99555206298828</v>
+        <v>53.99553298950195</v>
       </c>
       <c r="C149" t="n">
         <v>68.55999755859375</v>
@@ -4262,7 +4262,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>54.08217239379883</v>
+        <v>54.08217620849609</v>
       </c>
       <c r="C150" t="n">
         <v>68.66999816894531</v>
@@ -4316,7 +4316,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>53.56421661376953</v>
+        <v>53.56422805786133</v>
       </c>
       <c r="C152" t="n">
         <v>67.51999664306641</v>
@@ -4343,7 +4343,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>50.10540390014648</v>
+        <v>50.10540771484375</v>
       </c>
       <c r="C153" t="n">
         <v>63.15999984741211</v>
@@ -4370,7 +4370,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>48.71403503417969</v>
+        <v>48.71401977539062</v>
       </c>
       <c r="C154" t="n">
         <v>60.91999816894531</v>
@@ -4424,7 +4424,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>36.0637321472168</v>
+        <v>36.06372451782227</v>
       </c>
       <c r="C156" t="n">
         <v>45.09999847412109</v>
@@ -4451,7 +4451,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>29.16596221923828</v>
+        <v>29.16595077514648</v>
       </c>
       <c r="C157" t="n">
         <v>36.08000183105469</v>
@@ -4507,7 +4507,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>36.0290641784668</v>
+        <v>36.02907180786133</v>
       </c>
       <c r="C159" t="n">
         <v>44.06000137329102</v>
@@ -4536,7 +4536,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.62837982177734</v>
+        <v>35.62837219238281</v>
       </c>
       <c r="C160" t="n">
         <v>43.56999969482422</v>
@@ -4594,7 +4594,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>28.3669548034668</v>
+        <v>28.3669605255127</v>
       </c>
       <c r="C162" t="n">
         <v>34.68999862670898</v>
@@ -4623,7 +4623,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>32.96085357666016</v>
+        <v>32.96084976196289</v>
       </c>
       <c r="C163" t="n">
         <v>39.7400016784668</v>
@@ -4652,7 +4652,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>33.15160751342773</v>
+        <v>33.15161895751953</v>
       </c>
       <c r="C164" t="n">
         <v>39.97000122070312</v>
@@ -4766,7 +4766,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>30.49489402770996</v>
+        <v>30.49490165710449</v>
       </c>
       <c r="C168" t="n">
         <v>36.20000076293945</v>
@@ -4793,7 +4793,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>34.3366813659668</v>
+        <v>34.33667755126953</v>
       </c>
       <c r="C169" t="n">
         <v>40.20000076293945</v>
@@ -4847,7 +4847,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>23.4805965423584</v>
+        <v>23.48060035705566</v>
       </c>
       <c r="C171" t="n">
         <v>27.09000015258789</v>
@@ -4874,7 +4874,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>11.69263172149658</v>
+        <v>11.69262790679932</v>
       </c>
       <c r="C172" t="n">
         <v>13.48999977111816</v>
@@ -4901,7 +4901,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>14.57894992828369</v>
+        <v>14.57894706726074</v>
       </c>
       <c r="C173" t="n">
         <v>16.81999969482422</v>
@@ -4955,7 +4955,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>16.04861640930176</v>
+        <v>16.04862213134766</v>
       </c>
       <c r="C175" t="n">
         <v>18.38999938964844</v>
@@ -4982,7 +4982,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>15.83044624328613</v>
+        <v>15.83044719696045</v>
       </c>
       <c r="C176" t="n">
         <v>18.13999938964844</v>
@@ -5009,7 +5009,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>16.58967590332031</v>
+        <v>16.58967399597168</v>
       </c>
       <c r="C177" t="n">
         <v>19.01000022888184</v>
@@ -5036,7 +5036,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>13.66880321502686</v>
+        <v>13.66880512237549</v>
       </c>
       <c r="C178" t="n">
         <v>15.5600004196167</v>
@@ -5090,7 +5090,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>18.26313972473145</v>
+        <v>18.26313591003418</v>
       </c>
       <c r="C180" t="n">
         <v>20.79000091552734</v>
@@ -5117,7 +5117,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>19.29273223876953</v>
+        <v>19.29273414611816</v>
       </c>
       <c r="C181" t="n">
         <v>21.82999992370605</v>
@@ -5144,7 +5144,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>19.62856483459473</v>
+        <v>19.62856101989746</v>
       </c>
       <c r="C182" t="n">
         <v>22.20999908447266</v>
@@ -5171,7 +5171,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>24.78178215026855</v>
+        <v>24.78178405761719</v>
       </c>
       <c r="C183" t="n">
         <v>27.90999984741211</v>
@@ -5306,7 +5306,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>25.70121002197266</v>
+        <v>25.70121192932129</v>
       </c>
       <c r="C188" t="n">
         <v>28.82999992370605</v>
@@ -5335,7 +5335,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>25.10792541503906</v>
+        <v>25.10792350769043</v>
       </c>
       <c r="C189" t="n">
         <v>28.04000091552734</v>
@@ -5364,7 +5364,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>26.54061317443848</v>
+        <v>26.54061508178711</v>
       </c>
       <c r="C190" t="n">
         <v>29.63999938964844</v>
@@ -5393,7 +5393,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>28.88664817810059</v>
+        <v>28.88664436340332</v>
       </c>
       <c r="C191" t="n">
         <v>32.2599983215332</v>
@@ -5422,7 +5422,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>25.78972816467285</v>
+        <v>25.78972434997559</v>
       </c>
       <c r="C192" t="n">
         <v>28.68000030517578</v>
@@ -5451,7 +5451,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>26.93173789978027</v>
+        <v>26.93173980712891</v>
       </c>
       <c r="C193" t="n">
         <v>29.95000076293945</v>
@@ -5480,7 +5480,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>35.13265991210938</v>
+        <v>35.13265228271484</v>
       </c>
       <c r="C194" t="n">
         <v>39.06999969482422</v>
@@ -5567,7 +5567,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>35.18792343139648</v>
+        <v>35.18793106079102</v>
       </c>
       <c r="C197" t="n">
         <v>39.0099983215332</v>
@@ -5625,7 +5625,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>32.37385940551758</v>
+        <v>32.37386322021484</v>
       </c>
       <c r="C199" t="n">
         <v>35.7599983215332</v>
@@ -5654,7 +5654,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>33.52360534667969</v>
+        <v>33.52361297607422</v>
       </c>
       <c r="C200" t="n">
         <v>37.02999877929688</v>
@@ -5683,7 +5683,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>34.53755950927734</v>
+        <v>34.53755569458008</v>
       </c>
       <c r="C201" t="n">
         <v>38.15000152587891</v>
@@ -5712,7 +5712,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>32.65069580078125</v>
+        <v>32.65070343017578</v>
       </c>
       <c r="C202" t="n">
         <v>35.90000152587891</v>
@@ -5770,7 +5770,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>46.88421630859375</v>
+        <v>46.88420867919922</v>
       </c>
       <c r="C204" t="n">
         <v>51.54999923706055</v>
@@ -5886,7 +5886,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>45.02058029174805</v>
+        <v>45.02058410644531</v>
       </c>
       <c r="C208" t="n">
         <v>49.09999847412109</v>
@@ -5915,7 +5915,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>45.24981307983398</v>
+        <v>45.24980926513672</v>
       </c>
       <c r="C209" t="n">
         <v>49.34999847412109</v>
@@ -5944,7 +5944,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>39.27152252197266</v>
+        <v>39.27153015136719</v>
       </c>
       <c r="C210" t="n">
         <v>42.83000183105469</v>
@@ -5973,7 +5973,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>45.28386306762695</v>
+        <v>45.28385925292969</v>
       </c>
       <c r="C211" t="n">
         <v>49.11999893188477</v>
@@ -6031,7 +6031,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>54.35538864135742</v>
+        <v>54.35538482666016</v>
       </c>
       <c r="C213" t="n">
         <v>58.95999908447266</v>
@@ -6118,7 +6118,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>48.17615127563477</v>
+        <v>48.17615509033203</v>
       </c>
       <c r="C216" t="n">
         <v>52.04000091552734</v>
@@ -6176,7 +6176,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>45.30181121826172</v>
+        <v>45.30181503295898</v>
       </c>
       <c r="C218" t="n">
         <v>48.70000076293945</v>
@@ -6234,7 +6234,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>51.27590560913086</v>
+        <v>51.27590942382812</v>
       </c>
       <c r="C220" t="n">
         <v>54.81000137329102</v>
@@ -6263,7 +6263,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>44.41853713989258</v>
+        <v>44.41854095458984</v>
       </c>
       <c r="C221" t="n">
         <v>47.47999954223633</v>
@@ -6321,7 +6321,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.41927337646484</v>
+        <v>44.41928863525391</v>
       </c>
       <c r="C223" t="n">
         <v>47.18000030517578</v>
@@ -6350,7 +6350,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>45.46432876586914</v>
+        <v>45.46432495117188</v>
       </c>
       <c r="C224" t="n">
         <v>48.29000091552734</v>
@@ -6379,7 +6379,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>41.41593933105469</v>
+        <v>41.41594314575195</v>
       </c>
       <c r="C225" t="n">
         <v>43.9900016784668</v>
@@ -6408,7 +6408,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>39.75382232666016</v>
+        <v>39.75381851196289</v>
       </c>
       <c r="C226" t="n">
         <v>41.95000076293945</v>
@@ -6437,7 +6437,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>37.97224044799805</v>
+        <v>37.97224426269531</v>
       </c>
       <c r="C227" t="n">
         <v>40.06999969482422</v>
@@ -6466,7 +6466,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>41.63963317871094</v>
+        <v>41.6396369934082</v>
       </c>
       <c r="C228" t="n">
         <v>43.93999862670898</v>
@@ -6495,7 +6495,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>36.56316375732422</v>
+        <v>36.56315994262695</v>
       </c>
       <c r="C229" t="n">
         <v>38.34000015258789</v>
@@ -6524,7 +6524,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>38.41325759887695</v>
+        <v>38.41325378417969</v>
       </c>
       <c r="C230" t="n">
         <v>40.27999877929688</v>
@@ -6553,7 +6553,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>40.00590896606445</v>
+        <v>40.00590515136719</v>
       </c>
       <c r="C231" t="n">
         <v>41.65999984741211</v>
@@ -6582,7 +6582,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>40.14034271240234</v>
+        <v>40.14034652709961</v>
       </c>
       <c r="C232" t="n">
         <v>41.79999923706055</v>
@@ -6611,7 +6611,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>31.92982292175293</v>
+        <v>31.92981910705566</v>
       </c>
       <c r="C233" t="n">
         <v>33.25</v>
@@ -6640,7 +6640,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>31.73776054382324</v>
+        <v>31.73776245117188</v>
       </c>
       <c r="C234" t="n">
         <v>33.04999923706055</v>
